--- a/louvers/files/reference_xls/price_xls/slouver.xlsx
+++ b/louvers/files/reference_xls/price_xls/slouver.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10208"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10308"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/snigdhagoel/Documents/Vibrant Technik/vibrant-technik/offer-generator-test/files/reference_xls/price_xls/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/snigdhagoel/Documents/Vibrant Technik/vibrant-technik/offer-generator-test/louvers/files/reference_xls/price_xls/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F2F02484-42BD-A544-A62F-B8181DDBABF4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C35A59FB-7AA9-8F4A-AD4B-2C1792C4DDB4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="660" windowWidth="28800" windowHeight="15940" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -957,9 +957,6 @@
     <xf numFmtId="1" fontId="7" fillId="4" borderId="35" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
@@ -967,6 +964,9 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="36" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
@@ -1355,39 +1355,39 @@
       </c>
       <c r="B2" s="24">
         <f>C2/10.76391</f>
-        <v>67.749040767910245</v>
+        <v>74.52394484470129</v>
       </c>
       <c r="C2" s="2">
         <f>((((1000/133.7)*2)*50/1000)*'Per m weight'!B5)*A9</f>
-        <v>729.24457741211677</v>
+        <v>802.16903515332854</v>
       </c>
       <c r="D2" s="25">
         <f>+A9*'Per m weight'!B5</f>
-        <v>975</v>
+        <v>1072.5</v>
       </c>
       <c r="E2" s="30">
         <f>F2/10.76391</f>
-        <v>78.78866010329665</v>
+        <v>85.563564180087681</v>
       </c>
       <c r="F2" s="3">
         <f>C2+(('Per m weight'!C5/25.4)*39.37)*(((1000/133.7)*2)*50/1000)*'Per m weight'!G3</f>
-        <v>848.07404637247578</v>
+        <v>920.99850411368755</v>
       </c>
       <c r="G2" s="31">
         <f>+D2+((('Per m weight'!C5/25.4)*39.37008)*'Per m weight'!G3)</f>
-        <v>1133.8753228346457</v>
+        <v>1231.3753228346457</v>
       </c>
       <c r="H2" s="27">
         <f>I2/10.76391</f>
-        <v>94.244127172837608</v>
+        <v>101.01903124962865</v>
       </c>
       <c r="I2" s="4">
         <f>C2+(('Per m weight'!C5/25.4)*39.37)*(((1000/133.7)*2)*50/1000)*'Per m weight'!G4</f>
-        <v>1014.4353029169783</v>
+        <v>1087.3597606581902</v>
       </c>
       <c r="J2" s="9">
         <f>+D2+((('Per m weight'!C5/25.4)*39.37008)*'Per m weight'!G4)</f>
-        <v>1356.3007748031496</v>
+        <v>1453.8007748031496</v>
       </c>
     </row>
     <row r="3" spans="1:10" x14ac:dyDescent="0.2">
@@ -1396,39 +1396,39 @@
       </c>
       <c r="B3" s="24">
         <f>C3/10.76391</f>
-        <v>691.96749713338045</v>
+        <v>761.16424684671847</v>
       </c>
       <c r="C3" s="2">
         <f>((1000/B9)*'Per m weight'!B3)*A9</f>
-        <v>7448.2758620689647</v>
+        <v>8193.1034482758605</v>
       </c>
       <c r="D3" s="25">
         <f>+A9*'Per m weight'!B3</f>
-        <v>324</v>
+        <v>356.4</v>
       </c>
       <c r="E3" s="30">
         <f>F3/10.76391</f>
-        <v>791.27744856463039</v>
+        <v>860.4741982779683</v>
       </c>
       <c r="F3" s="3">
         <f>C3+(((('Per m weight'!C3*0.03937)*39.37)*(1000/B9))*'Per m weight'!G3)</f>
-        <v>8517.2392413793095</v>
+        <v>9262.0668275862045</v>
       </c>
       <c r="G3" s="31">
         <f>+D3+((('Per m weight'!C3/25.4)*39.37008)*'Per m weight'!G3)</f>
-        <v>370.50009448818901</v>
+        <v>402.90009448818898</v>
       </c>
       <c r="H3" s="27">
         <f t="shared" ref="H3:H4" si="0">I3/10.76391</f>
-        <v>930.31138056838017</v>
+        <v>999.50813028171808</v>
       </c>
       <c r="I3" s="4">
         <f>C3+(((('Per m weight'!C3*0.03937)*39.37)*(1000/B9))*'Per m weight'!G4)</f>
-        <v>10013.787972413793</v>
+        <v>10758.615558620688</v>
       </c>
       <c r="J3" s="9">
         <f>+D3+((('Per m weight'!C3/25.4)*39.37008)*'Per m weight'!G4)</f>
-        <v>435.60022677165358</v>
+        <v>468.00022677165356</v>
       </c>
     </row>
     <row r="4" spans="1:10" ht="17" thickBot="1" x14ac:dyDescent="0.25">
@@ -1437,39 +1437,39 @@
       </c>
       <c r="B4" s="33">
         <f>C4/10.76391</f>
-        <v>691.96749713338045</v>
+        <v>761.16424684671847</v>
       </c>
       <c r="C4" s="34">
         <f>((1000/B9)*'Per m weight'!B3)*A9</f>
-        <v>7448.2758620689647</v>
+        <v>8193.1034482758605</v>
       </c>
       <c r="D4" s="35">
         <f>+A9*'Per m weight'!B3</f>
-        <v>324</v>
+        <v>356.4</v>
       </c>
       <c r="E4" s="36">
         <f>F4/10.76391</f>
-        <v>824.3807657083803</v>
+        <v>893.5775154217182</v>
       </c>
       <c r="F4" s="37">
         <f>C4+(((('Per m weight'!C4*0.03937)*39.37)*(1000/B9))*'Per m weight'!G3)</f>
-        <v>8873.5603678160915</v>
+        <v>9618.3879540229864</v>
       </c>
       <c r="G4" s="38">
         <f>+D4+((('Per m weight'!C4/25.4)*39.37008)*'Per m weight'!G3)</f>
-        <v>386.00012598425195</v>
+        <v>418.40012598425193</v>
       </c>
       <c r="H4" s="39">
         <f t="shared" si="0"/>
-        <v>1009.7593417133801</v>
+        <v>1078.9560914267179</v>
       </c>
       <c r="I4" s="40">
         <f>C4+(((('Per m weight'!C4*0.03937)*39.37)*(1000/B9))*'Per m weight'!G4)</f>
-        <v>10868.958675862068</v>
+        <v>11613.786262068963</v>
       </c>
       <c r="J4" s="41">
         <f>+D4+((('Per m weight'!C4/25.4)*39.37008)*'Per m weight'!G4)</f>
-        <v>472.80030236220472</v>
+        <v>505.2003023622047</v>
       </c>
     </row>
     <row r="5" spans="1:10" x14ac:dyDescent="0.2">
@@ -1478,29 +1478,29 @@
       </c>
       <c r="B5" s="43">
         <f>SUM(B2:B3)</f>
-        <v>759.71653790129074</v>
+        <v>835.68819169141977</v>
       </c>
       <c r="C5" s="44">
         <f>SUM(C2:C3)</f>
-        <v>8177.5204394810817</v>
+        <v>8995.2724834291894</v>
       </c>
       <c r="D5" s="45"/>
       <c r="E5" s="46">
         <f>SUM(E2:E3)</f>
-        <v>870.06610866792698</v>
+        <v>946.03776245805602</v>
       </c>
       <c r="F5" s="47">
         <f>SUM(F2:F3)</f>
-        <v>9365.3132877517855</v>
+        <v>10183.065331699892</v>
       </c>
       <c r="G5" s="48"/>
       <c r="H5" s="49">
         <f>SUM(H2:H3)</f>
-        <v>1024.5555077412178</v>
+        <v>1100.5271615313468</v>
       </c>
       <c r="I5" s="50">
         <f>SUM(I2:I3)</f>
-        <v>11028.223275330771</v>
+        <v>11845.975319278878</v>
       </c>
       <c r="J5" s="51"/>
     </row>
@@ -1510,29 +1510,29 @@
       </c>
       <c r="B6" s="53">
         <f>SUM(B2,B4)</f>
-        <v>759.71653790129074</v>
+        <v>835.68819169141977</v>
       </c>
       <c r="C6" s="54">
         <f>SUM(C2,C4)</f>
-        <v>8177.5204394810817</v>
+        <v>8995.2724834291894</v>
       </c>
       <c r="D6" s="55"/>
       <c r="E6" s="56">
         <f>SUM(E2,E4)</f>
-        <v>903.169425811677</v>
+        <v>979.14107960180593</v>
       </c>
       <c r="F6" s="57">
         <f>SUM(F2,F4)</f>
-        <v>9721.6344141885675</v>
+        <v>10539.386458136674</v>
       </c>
       <c r="G6" s="58"/>
       <c r="H6" s="59">
         <f>SUM(H2,H4)</f>
-        <v>1104.0034688862177</v>
+        <v>1179.9751226763465</v>
       </c>
       <c r="I6" s="60">
         <f>SUM(I2,I4)</f>
-        <v>11883.393978779046</v>
+        <v>12701.146022727153</v>
       </c>
       <c r="J6" s="61"/>
     </row>
@@ -1547,7 +1547,7 @@
     </row>
     <row r="9" spans="1:10" ht="17" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A9" s="18">
-        <v>750</v>
+        <v>825</v>
       </c>
       <c r="B9" s="19">
         <v>43.5</v>
@@ -1571,11 +1571,11 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:7" ht="17" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="65" t="s">
+      <c r="A1" s="64" t="s">
         <v>16</v>
       </c>
-      <c r="B1" s="65"/>
-      <c r="C1" s="65"/>
+      <c r="B1" s="64"/>
+      <c r="C1" s="64"/>
     </row>
     <row r="2" spans="1:7" ht="32" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A2" s="10" t="s">
@@ -1589,10 +1589,10 @@
       </c>
     </row>
     <row r="3" spans="1:7" ht="17" x14ac:dyDescent="0.2">
-      <c r="A3" s="63" t="s">
+      <c r="A3" s="62" t="s">
         <v>22</v>
       </c>
-      <c r="B3" s="64">
+      <c r="B3" s="63">
         <v>0.432</v>
       </c>
       <c r="C3" s="15">
@@ -1601,27 +1601,27 @@
       <c r="D3" t="s">
         <v>23</v>
       </c>
-      <c r="E3" s="62" t="s">
+      <c r="E3" s="65" t="s">
         <v>20</v>
       </c>
-      <c r="F3" s="62"/>
+      <c r="F3" s="65"/>
       <c r="G3">
         <v>0.25</v>
       </c>
     </row>
     <row r="4" spans="1:7" ht="17" x14ac:dyDescent="0.2">
-      <c r="A4" s="63"/>
-      <c r="B4" s="64"/>
+      <c r="A4" s="62"/>
+      <c r="B4" s="63"/>
       <c r="C4" s="15">
         <v>160</v>
       </c>
       <c r="D4" t="s">
         <v>24</v>
       </c>
-      <c r="E4" s="62" t="s">
+      <c r="E4" s="65" t="s">
         <v>21</v>
       </c>
-      <c r="F4" s="62"/>
+      <c r="F4" s="65"/>
       <c r="G4">
         <v>0.6</v>
       </c>
